--- a/main/ig/observations-summary.xlsx
+++ b/main/ig/observations-summary.xlsx
@@ -230,7 +230,7 @@
     <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-signe-vital-cisis (required)</t>
   </si>
   <si>
-    <t>fr-Observation-vital-signs-panel-document</t>
+    <t>fr-observation-vital-signs-panel-document</t>
   </si>
   <si>
     <t>Observation - FR Observation Vital Signs Panel Document</t>

--- a/main/ig/observations-summary.xlsx
+++ b/main/ig/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="76">
   <si>
     <t>Profile</t>
   </si>
@@ -68,130 +68,121 @@
     <t>optional</t>
   </si>
   <si>
-    <t>fr-observation-antenatal-testing-surveillance-battery-document</t>
-  </si>
-  <si>
-    <t>Observation - FR Observation Antenatal Testing And Surveillance Battery Document</t>
-  </si>
-  <si>
-    <t>LOINC#XX-ANTENATALTESTINGBATTERY</t>
+    <t>fr-observation-birth-event-document</t>
+  </si>
+  <si>
+    <t>Observation - FR Observation Birth Event Document</t>
+  </si>
+  <si>
+    <t>SNOMED CT#118215003</t>
+  </si>
+  <si>
+    <t>dateTimeĵ</t>
+  </si>
+  <si>
+    <t>fr-observation-blood-product-transfusion-document</t>
+  </si>
+  <si>
+    <t>Observation - FR Blood Product Transfusion Document</t>
+  </si>
+  <si>
+    <t>TerminologieCISIS - Terminologie des concepts non trouvés dans les autres terminologies#MED-145</t>
+  </si>
+  <si>
+    <t>fr-observation-contra-indications-document</t>
+  </si>
+  <si>
+    <t>Observation - FR Observation Contra Indications Document</t>
+  </si>
+  <si>
+    <t>null#64100-1</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1 (example)</t>
+  </si>
+  <si>
+    <t>CodeableConceptĵ</t>
+  </si>
+  <si>
+    <t>fr-observation-medical-summary-document</t>
+  </si>
+  <si>
+    <t>Observation - FR Observation Medical Summary Document</t>
+  </si>
+  <si>
+    <t>TerminologieCISIS - Terminologie des concepts non trouvés dans les autres terminologies#MED-142</t>
+  </si>
+  <si>
+    <t>stringĵ</t>
+  </si>
+  <si>
+    <t>fr-observation-microorganism-detection-document</t>
+  </si>
+  <si>
+    <t>Observation - FR Observation Microorganism Detection Document</t>
+  </si>
+  <si>
+    <t>TerminologieCISIS - Terminologie des concepts non trouvés dans les autres terminologies#MED-309</t>
+  </si>
+  <si>
+    <t>fr-observation-multiresistant-microorganism-document</t>
+  </si>
+  <si>
+    <t>Observation - FR Observation Multiresistant Microorganisms Identification Document</t>
+  </si>
+  <si>
+    <t>TerminologieCISIS - Terminologie des concepts non trouvés dans les autres terminologies#MED-144</t>
+  </si>
+  <si>
+    <t>fr-observation-pain-score-document</t>
+  </si>
+  <si>
+    <t>Observation - FR Observation Pain Score Document</t>
+  </si>
+  <si>
+    <t>null#38208-5</t>
+  </si>
+  <si>
+    <t>integerĵ</t>
+  </si>
+  <si>
+    <t>fr-observation-pregnancy-history-document</t>
+  </si>
+  <si>
+    <t>Observation - FR Observation Pregnancy History Document</t>
+  </si>
+  <si>
+    <t>null#118185001</t>
+  </si>
+  <si>
+    <t>Periodĵ</t>
+  </si>
+  <si>
+    <t>fr-observation-radiation-exposure-document</t>
+  </si>
+  <si>
+    <t>Observation - FR Observation Radiation Exposure Document</t>
+  </si>
+  <si>
+    <t>LOINC#73569-6</t>
+  </si>
+  <si>
+    <t>Quantity, CodeableConcept, string, boolean, integer, Range, Ratio, SampledData, time, dateTime, Period</t>
+  </si>
+  <si>
+    <t>fr-observation-social-history-document</t>
+  </si>
+  <si>
+    <t>Observation - FR Observation Social History Document</t>
+  </si>
+  <si>
+    <t>Observation Category Codes#social-history</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-social-history-code-cisis (required)</t>
   </si>
   <si>
     <t>dateTime, Period, Timing, instant</t>
-  </si>
-  <si>
-    <t>Quantity, CodeableConcept, string, boolean, integer, Range, Ratio, SampledData, time, dateTime, Period</t>
-  </si>
-  <si>
-    <t>fr-observation-birth-event-document</t>
-  </si>
-  <si>
-    <t>Observation - FR Observation Birth Event Document</t>
-  </si>
-  <si>
-    <t>SNOMED CT#118215003</t>
-  </si>
-  <si>
-    <t>dateTimeĵ</t>
-  </si>
-  <si>
-    <t>fr-observation-blood-product-transfusion-document</t>
-  </si>
-  <si>
-    <t>Observation - FR Blood Product Transfusion Document</t>
-  </si>
-  <si>
-    <t>TerminologieCISIS - Terminologie des concepts non trouvés dans les autres terminologies#MED-145</t>
-  </si>
-  <si>
-    <t>fr-observation-contra-indications-document</t>
-  </si>
-  <si>
-    <t>Observation - FR Observation Contra Indications Document</t>
-  </si>
-  <si>
-    <t>null#64100-1</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1 (example)</t>
-  </si>
-  <si>
-    <t>CodeableConceptĵ</t>
-  </si>
-  <si>
-    <t>fr-observation-medical-summary-document</t>
-  </si>
-  <si>
-    <t>Observation - FR Observation Medical Summary Document</t>
-  </si>
-  <si>
-    <t>TerminologieCISIS - Terminologie des concepts non trouvés dans les autres terminologies#MED-142</t>
-  </si>
-  <si>
-    <t>stringĵ</t>
-  </si>
-  <si>
-    <t>fr-observation-microorganism-detection-document</t>
-  </si>
-  <si>
-    <t>Observation - FR Observation Microorganism Detection Document</t>
-  </si>
-  <si>
-    <t>TerminologieCISIS - Terminologie des concepts non trouvés dans les autres terminologies#MED-309</t>
-  </si>
-  <si>
-    <t>fr-observation-multiresistant-microorganism-document</t>
-  </si>
-  <si>
-    <t>Observation - FR Observation Multiresistant Microorganisms Identification Document</t>
-  </si>
-  <si>
-    <t>TerminologieCISIS - Terminologie des concepts non trouvés dans les autres terminologies#MED-144</t>
-  </si>
-  <si>
-    <t>fr-observation-pain-score-document</t>
-  </si>
-  <si>
-    <t>Observation - FR Observation Pain Score Document</t>
-  </si>
-  <si>
-    <t>null#38208-5</t>
-  </si>
-  <si>
-    <t>integerĵ</t>
-  </si>
-  <si>
-    <t>fr-observation-pregnancy-history-document</t>
-  </si>
-  <si>
-    <t>Observation - FR Observation Pregnancy History Document</t>
-  </si>
-  <si>
-    <t>null#118185001</t>
-  </si>
-  <si>
-    <t>Periodĵ</t>
-  </si>
-  <si>
-    <t>fr-observation-radiation-exposure-document</t>
-  </si>
-  <si>
-    <t>Observation - FR Observation Radiation Exposure Document</t>
-  </si>
-  <si>
-    <t>LOINC#73569-6</t>
-  </si>
-  <si>
-    <t>fr-observation-social-history-document</t>
-  </si>
-  <si>
-    <t>Observation - FR Observation Social History Document</t>
-  </si>
-  <si>
-    <t>Observation Category Codes#social-history</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-social-history-code-cisis (required)</t>
   </si>
   <si>
     <t>Quantityĵ, CodeableConceptĵ, stringĵ, booleanĵ, integerĵ, Rangeĵ, Ratioĵ, SampledDataĵ, timeĵ, dateTimeĵ, Periodĵ</t>
@@ -382,7 +373,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -478,7 +469,7 @@
         <v>21</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="I3" t="s" s="2">
         <v>17</v>
@@ -492,28 +483,28 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="B4" t="s" s="2">
+      <c r="C4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="C4" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s" s="2">
-        <v>25</v>
-      </c>
       <c r="F4" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>17</v>
@@ -527,28 +518,28 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s" s="2">
         <v>27</v>
       </c>
-      <c r="B5" t="s" s="2">
+      <c r="F5" t="s" s="2">
         <v>28</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E5" t="s" s="2">
-        <v>29</v>
-      </c>
-      <c r="F5" t="s" s="2">
-        <v>13</v>
       </c>
       <c r="G5" t="s" s="2">
         <v>15</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>17</v>
@@ -577,13 +568,13 @@
         <v>32</v>
       </c>
       <c r="F6" t="s" s="2">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="G6" t="s" s="2">
         <v>15</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>17</v>
@@ -597,19 +588,19 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="B7" t="s" s="2">
+      <c r="C7" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s" s="2">
         <v>36</v>
-      </c>
-      <c r="C7" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D7" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E7" t="s" s="2">
-        <v>37</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>13</v>
@@ -618,7 +609,7 @@
         <v>15</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>17</v>
@@ -632,19 +623,19 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s" s="2">
         <v>39</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="C8" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E8" t="s" s="2">
-        <v>41</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>13</v>
@@ -653,7 +644,7 @@
         <v>15</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>17</v>
@@ -667,28 +658,28 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s" s="2">
         <v>42</v>
       </c>
-      <c r="B9" t="s" s="2">
+      <c r="F9" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="H9" t="s" s="2">
         <v>43</v>
-      </c>
-      <c r="C9" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E9" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="F9" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G9" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="H9" t="s" s="2">
-        <v>38</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>17</v>
@@ -702,28 +693,28 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>45</v>
       </c>
-      <c r="B10" t="s" s="2">
+      <c r="C10" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="C10" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E10" t="s" s="2">
+      <c r="F10" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="G10" t="s" s="2">
         <v>47</v>
       </c>
-      <c r="F10" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="G10" t="s" s="2">
-        <v>26</v>
-      </c>
       <c r="H10" t="s" s="2">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>17</v>
@@ -737,28 +728,28 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>49</v>
       </c>
-      <c r="B11" t="s" s="2">
+      <c r="C11" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E11" t="s" s="2">
         <v>50</v>
       </c>
-      <c r="C11" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E11" t="s" s="2">
+      <c r="F11" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="H11" t="s" s="2">
         <v>51</v>
-      </c>
-      <c r="F11" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="G11" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="H11" t="s" s="2">
-        <v>13</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>17</v>
@@ -772,28 +763,28 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>53</v>
       </c>
-      <c r="B12" t="s" s="2">
+      <c r="C12" t="s" s="2">
         <v>54</v>
       </c>
-      <c r="C12" t="s" s="2">
-        <v>13</v>
-      </c>
       <c r="D12" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E12" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F12" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="F12" t="s" s="2">
-        <v>13</v>
-      </c>
       <c r="G12" t="s" s="2">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>17</v>
@@ -807,28 +798,28 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="F13" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="G13" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="B13" t="s" s="2">
+      <c r="H13" t="s" s="2">
         <v>57</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E13" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="F13" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="G13" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="H13" t="s" s="2">
-        <v>60</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>17</v>
@@ -842,13 +833,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>13</v>
@@ -857,13 +848,13 @@
         <v>13</v>
       </c>
       <c r="F14" t="s" s="2">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>17</v>
@@ -880,7 +871,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>13</v>
@@ -898,7 +889,7 @@
         <v>13</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>17</v>
@@ -912,10 +903,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s" s="2">
         <v>13</v>
@@ -924,16 +915,16 @@
         <v>13</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>13</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>17</v>
@@ -953,22 +944,22 @@
         <v>66</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="F17" t="s" s="2">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>17</v>
@@ -982,28 +973,28 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="F18" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>17</v>
@@ -1017,28 +1008,28 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>13</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F19" t="s" s="2">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>17</v>
@@ -1047,41 +1038,6 @@
         <v>13</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="D20" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="E20" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="F20" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="G20" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="H20" t="s" s="2">
-        <v>16</v>
-      </c>
-      <c r="I20" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="J20" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K20" t="s" s="2">
         <v>13</v>
       </c>
     </row>
